--- a/data/availability/projects/misr-italia-properties/solare.xlsx
+++ b/data/availability/projects/misr-italia-properties/solare.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,6 +943,206 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>5%+10% over 9 yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Loft</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Loft</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>145</v>
+      </c>
+      <c r="F11" t="n">
+        <v>145</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>220</v>
+      </c>
+      <c r="F12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>240</v>
+      </c>
+      <c r="F13" t="n">
+        <v>240</v>
+      </c>
+      <c r="G13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas (One Story)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
         </is>
       </c>
     </row>
@@ -957,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,7 +1259,6 @@
       <c r="G2" t="n">
         <v>115</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1116,7 +1315,6 @@
       <c r="G3" t="n">
         <v>135</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1173,7 +1371,6 @@
       <c r="G4" t="n">
         <v>174</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1230,7 +1427,6 @@
       <c r="G5" t="n">
         <v>174</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1287,7 +1483,6 @@
       <c r="G6" t="n">
         <v>188</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1344,7 +1539,6 @@
       <c r="G7" t="n">
         <v>207</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1401,7 +1595,6 @@
       <c r="G8" t="n">
         <v>109</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1458,7 +1651,6 @@
       <c r="G9" t="n">
         <v>129</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1478,6 +1670,234 @@
         </is>
       </c>
       <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Loft</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOL-OOV-WV-2B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>120</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Lagoon &amp; Pools</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Loft</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SOL-OOV-WV-3B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>145</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Lagoon &amp; Pools</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>15300000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SOL-OOV-SA-3B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Lagoon &amp; Pools</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>20600000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>solare</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOL-OOV-TWIN-4B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Olive Oasis Villas (One Story)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>240</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Lagoon &amp; Pools</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Dec 2028</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5% DP over 8 Yrs</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/data/availability/projects/misr-italia-properties/solare.xlsx
+++ b/data/availability/projects/misr-italia-properties/solare.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1707,7 +1707,6 @@
       <c r="G10" t="n">
         <v>120</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Lagoon &amp; Pools</t>
@@ -1718,7 +1717,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1764,7 +1763,6 @@
       <c r="G11" t="n">
         <v>145</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Lagoon &amp; Pools</t>
@@ -1775,7 +1773,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1821,7 +1819,6 @@
       <c r="G12" t="n">
         <v>220</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Lagoon &amp; Pools</t>
@@ -1832,7 +1829,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1878,7 +1875,6 @@
       <c r="G13" t="n">
         <v>240</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Lagoon &amp; Pools</t>
@@ -1889,7 +1885,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
